--- a/data/trans_orig/P70A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70A_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si dichos problemas de salud fueron causados por su trabajo en 2023</t>
+          <t>Población según si su ausencia en el trabajo por motivos de salud, fue debido a problemas de salud causados por su trabajo en 2023 (tasa de respuesta: 94,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31912</t>
+          <t>31456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -843,97 +843,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1153</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3249</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6017</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>34,3%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>1153</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6282</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>7133</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>35,82%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1153</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>6471</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>16852</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43095</t>
+          <t>42472</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62062</t>
+          <t>62079</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60273</t>
+          <t>59618</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72132</t>
+          <t>72377</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108674</t>
+          <t>110074</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130692</t>
+          <t>131052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16641</t>
+          <t>14424</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>21490</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25586</t>
+          <t>25483</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71684</t>
+          <t>72770</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88074</t>
+          <t>88090</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74534</t>
+          <t>74449</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87435</t>
+          <t>87083</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>153229</t>
+          <t>152724</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>171686</t>
+          <t>172446</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,92%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23118</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13909</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31046</t>
+          <t>32059</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7089</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>16994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>260843</t>
+          <t>259184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>368531</t>
+          <t>367941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74573</t>
+          <t>75783</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89202</t>
+          <t>89699</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>345802</t>
+          <t>345912</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>464949</t>
+          <t>467701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43024</t>
+          <t>44317</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>9463</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60566</t>
+          <t>60070</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76184</t>
+          <t>77047</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21680</t>
+          <t>20834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84405</t>
+          <t>83384</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38009</t>
+          <t>37334</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53568</t>
+          <t>53282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34808</t>
+          <t>35276</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45865</t>
+          <t>45870</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77693</t>
+          <t>76968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96611</t>
+          <t>95019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20305</t>
+          <t>20736</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14674</t>
+          <t>14426</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15752</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30703</t>
+          <t>31808</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22827</t>
+          <t>23659</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19467</t>
+          <t>20040</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35446</t>
+          <t>35670</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,62 +3158,62 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>980</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -3236,97 +3236,97 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>16,31%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>45,15%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2797</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>16,31%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>3535</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>9,63%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>44,98%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1014</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>3228</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -3466,97 +3466,97 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
           <t>852</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>852</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>852</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -3579,97 +3579,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -3692,97 +3692,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>466632</t>
+          <t>467555</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>606059</t>
+          <t>602534</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>271397</t>
+          <t>272838</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>301046</t>
+          <t>300493</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>759965</t>
+          <t>758757</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>921924</t>
+          <t>939866</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>16845</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>83324</t>
+          <t>82460</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>30027</t>
+          <t>29604</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>49106</t>
+          <t>49495</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>38175</t>
+          <t>32106</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>119360</t>
+          <t>119541</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>94187</t>
+          <t>93105</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>37210</t>
+          <t>37404</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>61315</t>
+          <t>60292</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>48195</t>
+          <t>43622</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>140240</t>
+          <t>141980</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70A_2023-Edad-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15286</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>30869</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>20741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31456</t>
+          <t>36598</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>13235</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16852</t>
+          <t>17725</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>44,08%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34880</t>
+          <t>40209</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34880</t>
+          <t>40209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34880</t>
+          <t>40209</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>53931</t>
+          <t>58099</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42472</t>
+          <t>46835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62079</t>
+          <t>65424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>67275</t>
+          <t>72014</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59618</t>
+          <t>64344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72377</t>
+          <t>77234</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>121206</t>
+          <t>130113</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>110074</t>
+          <t>115700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131052</t>
+          <t>139639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14424</t>
+          <t>15109</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21490</t>
+          <t>21162</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>19923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15348</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25483</t>
+          <t>28331</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69665</t>
+          <t>74751</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69665</t>
+          <t>74751</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69665</t>
+          <t>74751</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78120</t>
+          <t>83066</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78120</t>
+          <t>83066</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78120</t>
+          <t>83066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>147785</t>
+          <t>157817</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>147785</t>
+          <t>157817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147785</t>
+          <t>157817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>88298</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72770</t>
+          <t>78987</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88090</t>
+          <t>95315</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82112</t>
+          <t>91407</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74449</t>
+          <t>84493</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87083</t>
+          <t>97741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>163125</t>
+          <t>179705</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>152724</t>
+          <t>167609</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>172446</t>
+          <t>189147</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,71%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>22228</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>16380</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>23875</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>34447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14364</t>
+          <t>14460</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>96774</t>
+          <t>105066</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96774</t>
+          <t>105066</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96774</t>
+          <t>105066</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>99359</t>
+          <t>110578</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>99359</t>
+          <t>110578</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99359</t>
+          <t>110578</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>196133</t>
+          <t>215644</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>196133</t>
+          <t>215644</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>196133</t>
+          <t>215644</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>338160</t>
+          <t>104014</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>259184</t>
+          <t>91826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>367941</t>
+          <t>114963</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>82568</t>
+          <t>90041</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75783</t>
+          <t>80981</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89699</t>
+          <t>97478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>420728</t>
+          <t>194056</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>345912</t>
+          <t>178103</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>467701</t>
+          <t>206920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44317</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14555</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>22312</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>27674</t>
+          <t>28984</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>21082</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60070</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>25153</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>15912</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77047</t>
+          <t>36513</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20834</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>38518</t>
+          <t>40859</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>31112</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83384</t>
+          <t>54838</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>375109</t>
+          <t>142759</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>375109</t>
+          <t>142759</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>375109</t>
+          <t>142759</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>111811</t>
+          <t>121140</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111811</t>
+          <t>121140</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111811</t>
+          <t>121140</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>486920</t>
+          <t>263899</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>486920</t>
+          <t>263899</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>486920</t>
+          <t>263899</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>45749</t>
+          <t>47220</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37334</t>
+          <t>39044</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53282</t>
+          <t>55020</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>40781</t>
+          <t>45670</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35276</t>
+          <t>40019</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45870</t>
+          <t>51166</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>86530</t>
+          <t>92891</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76968</t>
+          <t>83074</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95019</t>
+          <t>103622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>71,49%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13032</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20736</t>
+          <t>20310</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14426</t>
+          <t>15446</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>24197</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>31808</t>
+          <t>32759</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>15696</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23659</t>
+          <t>22991</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>26940</t>
+          <t>27857</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20040</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35670</t>
+          <t>36526</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>74477</t>
+          <t>76777</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74477</t>
+          <t>76777</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74477</t>
+          <t>76777</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>61628</t>
+          <t>68167</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>61628</t>
+          <t>68167</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>61628</t>
+          <t>68167</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>136105</t>
+          <t>144944</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>136105</t>
+          <t>144944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>136105</t>
+          <t>144944</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,27 +3005,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3040,27 +3040,27 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>11203</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>719</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>719</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>11649</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>11649</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>11649</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>539529</t>
+          <t>321554</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>467555</t>
+          <t>302575</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>602534</t>
+          <t>339997</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>288086</t>
+          <t>316853</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>272838</t>
+          <t>301184</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>300493</t>
+          <t>332072</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>827615</t>
+          <t>638408</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>758757</t>
+          <t>612366</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>939866</t>
+          <t>662070</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>79,28%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>45996</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>34965</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>82460</t>
+          <t>63737</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>39038</t>
+          <t>42612</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>29604</t>
+          <t>34185</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>49495</t>
+          <t>56310</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>85034</t>
+          <t>90775</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>32106</t>
+          <t>73301</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>119541</t>
+          <t>107677</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>53004</t>
+          <t>56123</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>41392</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>93105</t>
+          <t>71549</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>47551</t>
+          <t>49786</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>37404</t>
+          <t>37426</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>60292</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>100556</t>
+          <t>105910</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>43622</t>
+          <t>88747</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>141980</t>
+          <t>127695</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>638529</t>
+          <t>425841</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>638529</t>
+          <t>425841</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>638529</t>
+          <t>425841</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>374675</t>
+          <t>409251</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>374675</t>
+          <t>409251</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>374675</t>
+          <t>409251</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1013204</t>
+          <t>835092</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1013204</t>
+          <t>835092</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1013204</t>
+          <t>835092</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
